--- a/output/laminas_comunales/comunal_m_miginterna_a_2019_biobio.xlsx
+++ b/output/laminas_comunales/comunal_m_miginterna_a_2019_biobio.xlsx
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2019. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2019. Escala comunal recortada a percentiles 3-97.</t>
         </is>
       </c>
     </row>
